--- a/docs/package/05_Delivery/Upload_Templates/Lead_Source_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Lead_Source_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t xml:space="preserve">Code</t>
   </si>
@@ -33,6 +33,9 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
+    <t xml:space="preserve">KYC Mode</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -105,6 +108,15 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
+    <t xml:space="preserve">One of the allowed values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full KYC, TFS confirmation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kycMode</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active when empty</t>
   </si>
   <si>
@@ -132,12 +144,6 @@
     <t xml:space="preserve">Master &gt; Insurance Management &gt; Lead Sources (no Upload button on this screen yet: a System Administrator uploads the file through the API route)</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/lead-source/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -168,10 +174,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -189,10 +195,10 @@
     <t xml:space="preserve">Where a prospect came from: the Source of the prospect form and of the lead upload (matched by code or name) and a lead assignment condition.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -200,7 +206,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -380,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -390,9 +396,10 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20" customHeight="1">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -414,22 +421,25 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -439,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -452,22 +462,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
@@ -475,16 +485,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +519,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -526,16 +536,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -543,16 +553,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +570,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -574,16 +584,33 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -593,7 +620,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -602,111 +629,103 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>55</v>
-      </c>
       <c r="B12" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>60</v>
+      </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
